--- a/data/trans_camb/IP19C07-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C07-Edad-trans_camb.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-71,7; 0,0</t>
+          <t>-71,49; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-74,12; 0,0</t>
+          <t>-74,35; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-57,7; 0,0</t>
+          <t>-52,59; 0,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-51,31; 0,0</t>
+          <t>-57,21; 0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-54,88; 0,0</t>
+          <t>-53,27; 0,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,0; 4,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,01</t>
+          <t>0,0; 5,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,35</t>
+          <t>0,0; 6,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 6,26</t>
+          <t>-1,89; 6,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 4,88</t>
+          <t>-2,29; 4,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 5,25</t>
+          <t>-2,7; 5,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 4,1</t>
+          <t>-0,64; 4,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,33</t>
+          <t>-0,8; 3,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 4,93</t>
+          <t>-0,42; 4,77</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,4; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-78,11; —</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 1,15</t>
+          <t>-10,37; 2,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,49; -3,36</t>
+          <t>-14,99; -3,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,72; -3,32</t>
+          <t>-14,62; -2,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 9,38</t>
+          <t>-1,15; 9,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 3,75</t>
+          <t>-5,11; 3,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 6,11</t>
+          <t>-2,75; 6,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 4,13</t>
+          <t>-4,29; 3,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,05; -1,0</t>
+          <t>-7,93; -0,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 0,88</t>
+          <t>-6,59; 1,03</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-71,23; 16,08</t>
+          <t>-69,32; 48,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-92,93; -29,12</t>
+          <t>-92,68; -30,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-90,55; -30,02</t>
+          <t>-91,74; -29,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 417,02</t>
+          <t>-23,8; 397,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-71,58; 186,79</t>
+          <t>-72,72; 169,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,82; 276,79</t>
+          <t>-44,22; 287,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,95; 77,64</t>
+          <t>-41,47; 70,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-78,96; -10,05</t>
+          <t>-78,48; -9,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,57; 21,06</t>
+          <t>-67,7; 22,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 5,27</t>
+          <t>-8,58; 5,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 5,92</t>
+          <t>-8,99; 5,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 0,16</t>
+          <t>-13,29; -0,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 5,52</t>
+          <t>-8,8; 5,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,36; -1,64</t>
+          <t>-14,18; -2,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,92; -4,98</t>
+          <t>-16,34; -4,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 3,06</t>
+          <t>-7,27; 2,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,44; -0,01</t>
+          <t>-9,44; -0,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,2; -4,35</t>
+          <t>-13,1; -4,79</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,36; 35,65</t>
+          <t>-39,62; 33,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,34; 37,7</t>
+          <t>-40,05; 40,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,81; 2,35</t>
+          <t>-59,11; -0,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,7; 43,24</t>
+          <t>-43,64; 37,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-69,92; -3,66</t>
+          <t>-68,81; -9,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-78,2; -32,98</t>
+          <t>-78,01; -32,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-33,29; 19,85</t>
+          <t>-34,97; 16,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,34; 0,28</t>
+          <t>-47,52; 0,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-63,5; -26,79</t>
+          <t>-62,81; -29,09</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 1,16</t>
+          <t>-6,6; 1,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,99; -0,41</t>
+          <t>-8,03; -0,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,38; -0,72</t>
+          <t>-8,19; -0,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 3,41</t>
+          <t>-3,89; 3,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -1,37</t>
+          <t>-7,2; -0,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,92; -1,11</t>
+          <t>-7,31; -1,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 1,39</t>
+          <t>-3,95; 1,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,61; -1,63</t>
+          <t>-6,88; -1,98</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,05; -2,2</t>
+          <t>-6,95; -2,04</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-46,71; 11,65</t>
+          <t>-45,46; 14,07</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,74; -4,1</t>
+          <t>-54,28; -4,24</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-57,5; -5,63</t>
+          <t>-55,66; -8,06</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 41,55</t>
+          <t>-32,63; 39,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-64,08; -14,62</t>
+          <t>-62,73; -11,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-62,67; -12,31</t>
+          <t>-62,02; -11,9</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-30,64; 13,27</t>
+          <t>-31,7; 11,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-52,34; -16,19</t>
+          <t>-53,69; -18,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-56,43; -22,85</t>
+          <t>-56,04; -20,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C07-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C07-Edad-trans_camb.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-71,49; 0,0</t>
+          <t>-71,16; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-74,35; 0,0</t>
+          <t>-71,92; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-52,59; 0,0</t>
+          <t>-53,78; 0,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-57,21; 0,0</t>
+          <t>-63,0; 0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-53,27; 0,0</t>
+          <t>-60,88; 0,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 5,5</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 4,87</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,69</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,93</t>
+          <t>0,0; 7,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 6,38</t>
+          <t>-2,24; 6,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 4,77</t>
+          <t>-2,54; 4,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 5,52</t>
+          <t>-2,49; 5,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,34</t>
+          <t>-0,73; 4,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,5</t>
+          <t>-0,78; 3,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 4,77</t>
+          <t>-0,38; 4,79</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-78,11; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 2,3</t>
+          <t>-10,69; 1,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,99; -3,66</t>
+          <t>-14,89; -3,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,62; -2,76</t>
+          <t>-14,16; -2,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 9,6</t>
+          <t>-1,24; 8,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 3,54</t>
+          <t>-5,35; 3,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 6,3</t>
+          <t>-2,97; 6,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 3,86</t>
+          <t>-4,3; 3,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,93; -0,89</t>
+          <t>-8,15; -1,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 1,03</t>
+          <t>-6,92; 0,63</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-69,32; 48,72</t>
+          <t>-70,79; 33,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-92,68; -30,74</t>
+          <t>-92,67; -39,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-91,74; -29,96</t>
+          <t>-91,28; -24,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,8; 397,61</t>
+          <t>-27,76; 362,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-72,72; 169,4</t>
+          <t>-69,5; 177,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,22; 287,69</t>
+          <t>-48,97; 336,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,47; 70,67</t>
+          <t>-42,44; 72,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-78,48; -9,64</t>
+          <t>-79,47; -14,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-67,7; 22,89</t>
+          <t>-65,57; 21,05</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 5,27</t>
+          <t>-9,02; 4,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 5,93</t>
+          <t>-9,35; 5,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,29; -0,28</t>
+          <t>-13,58; -0,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 5,14</t>
+          <t>-8,73; 4,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,18; -2,09</t>
+          <t>-14,16; -2,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,34; -4,58</t>
+          <t>-16,29; -5,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 2,6</t>
+          <t>-7,29; 2,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,44; -0,11</t>
+          <t>-9,56; 0,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,1; -4,79</t>
+          <t>-12,84; -4,34</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,62; 33,8</t>
+          <t>-39,84; 29,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-40,05; 40,47</t>
+          <t>-41,01; 36,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,11; -0,51</t>
+          <t>-58,43; 0,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,64; 37,92</t>
+          <t>-43,79; 33,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,81; -9,64</t>
+          <t>-71,08; -14,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-78,01; -32,2</t>
+          <t>-78,42; -37,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,97; 16,89</t>
+          <t>-34,95; 18,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,52; 0,03</t>
+          <t>-48,07; 1,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-62,81; -29,09</t>
+          <t>-62,35; -24,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 1,34</t>
+          <t>-6,23; 1,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,03; -0,55</t>
+          <t>-7,75; -0,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,19; -0,93</t>
+          <t>-8,13; -0,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 3,43</t>
+          <t>-3,38; 3,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,2; -0,97</t>
+          <t>-7,59; -1,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,31; -1,21</t>
+          <t>-7,37; -1,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 1,12</t>
+          <t>-3,88; 1,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,88; -1,98</t>
+          <t>-6,7; -1,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,95; -2,04</t>
+          <t>-6,93; -1,95</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-45,46; 14,07</t>
+          <t>-45,41; 11,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-54,28; -4,24</t>
+          <t>-54,44; -0,01</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-55,66; -8,06</t>
+          <t>-56,97; -3,72</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-32,63; 39,54</t>
+          <t>-28,93; 43,2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-62,73; -11,96</t>
+          <t>-63,7; -14,02</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-62,02; -11,9</t>
+          <t>-62,85; -11,88</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 11,17</t>
+          <t>-31,61; 13,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-53,69; -18,39</t>
+          <t>-53,27; -17,23</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-56,04; -20,89</t>
+          <t>-55,45; -18,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C07-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C07-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-19,67</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-19,67</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-19,67</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-71,16; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-71,92; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-71,7; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-74,12; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-53,78; 0,0</t>
+          <t>-57,7; 0,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-63,0; 0,0</t>
+          <t>-51,31; 0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-60,88; 0,0</t>
+          <t>-54,88; 0,0</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,67</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,17</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,91</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,96</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,24</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>2,19</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>1,57</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,5</t>
+          <t>-2,01; 6,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,87</t>
+          <t>-2,15; 4,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,44</t>
+          <t>-2,44; 5,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 6,02</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 4,86</t>
+          <t>0,0; 6,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 5,53</t>
+          <t>0,0; 7,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,01</t>
+          <t>-0,66; 4,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,36</t>
+          <t>-0,5; 3,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,79</t>
+          <t>-0,47; 4,96</t>
         </is>
       </c>
     </row>
@@ -946,34 +946,34 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>101,46%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>71,12%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>55,38%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>101,46%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>71,12%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>56,61%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>178,73%</t>
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>201,42%</t>
+          <t>196,29%</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
+          <t>-80,4; —</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>-100,0; —</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,06</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,46</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,01</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-4,18</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-8,55</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-7,96</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,06</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>-8,09</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,86</t>
+          <t>-2,72</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 1,68</t>
+          <t>-1,2; 9,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,89; -3,89</t>
+          <t>-5,06; 3,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,16; -2,7</t>
+          <t>-2,94; 6,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 8,92</t>
+          <t>-11,56; 1,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 3,26</t>
+          <t>-14,49; -3,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 6,63</t>
+          <t>-14,73; -3,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 3,94</t>
+          <t>-4,41; 4,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,15; -1,02</t>
+          <t>-8,05; -1,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 0,63</t>
+          <t>-6,57; 1,17</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>86,87%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-9,93%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-37,81%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-77,23%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-71,91%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>86,87%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-9,93%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>-73,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-36,76%</t>
+          <t>-34,95%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-70,79; 33,03</t>
+          <t>-23,71; 417,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-92,67; -39,59</t>
+          <t>-71,58; 186,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-91,28; -24,77</t>
+          <t>-46,71; 295,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 362,3</t>
+          <t>-71,23; 16,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,5; 177,42</t>
+          <t>-92,93; -29,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,97; 336,3</t>
+          <t>-90,97; -29,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-42,44; 72,81</t>
+          <t>-41,95; 77,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-79,47; -14,8</t>
+          <t>-78,96; -10,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,57; 21,05</t>
+          <t>-65,92; 23,23</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,98</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-8,16</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-10,48</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-2,2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,74</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-6,37</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,98</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-8,16</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-10,67</t>
+          <t>-6,14</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-8,77</t>
+          <t>-8,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 4,47</t>
+          <t>-8,27; 5,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 5,44</t>
+          <t>-14,36; -1,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,58; -0,09</t>
+          <t>-15,73; -4,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 4,98</t>
+          <t>-9,57; 5,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,16; -2,16</t>
+          <t>-9,75; 5,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,29; -5,89</t>
+          <t>-12,89; 0,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 2,84</t>
+          <t>-6,63; 3,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 0,15</t>
+          <t>-9,44; -0,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,84; -4,34</t>
+          <t>-12,93; -3,83</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-11,46%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-47,3%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-60,76%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-11,54%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-9,13%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-33,41%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-11,46%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-47,3%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-61,88%</t>
+          <t>-32,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-48,39%</t>
+          <t>-46,82%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,84; 29,4</t>
+          <t>-40,7; 43,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,01; 36,43</t>
+          <t>-69,92; -3,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,43; 0,23</t>
+          <t>-77,81; -30,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,79; 33,32</t>
+          <t>-40,36; 35,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,08; -14,37</t>
+          <t>-41,34; 37,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-78,42; -37,4</t>
+          <t>-58,43; 4,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,95; 18,44</t>
+          <t>-33,29; 19,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,07; 1,08</t>
+          <t>-47,34; 0,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-62,35; -24,92</t>
+          <t>-62,36; -24,6</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,14</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-4,34</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-3,96</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-2,54</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-4,05</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-4,47</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-4,34</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,26</t>
+          <t>-4,28</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,46</t>
+          <t>-4,18</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 1,17</t>
+          <t>-3,88; 3,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,75; -0,2</t>
+          <t>-7,89; -1,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,13; -0,42</t>
+          <t>-7,66; -0,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 3,51</t>
+          <t>-6,7; 1,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,59; -1,17</t>
+          <t>-7,99; -0,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,37; -1,02</t>
+          <t>-8,17; -0,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 1,36</t>
+          <t>-3,82; 1,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,7; -1,74</t>
+          <t>-6,61; -1,63</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,93; -1,95</t>
+          <t>-6,78; -1,81</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-1,37%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-43,3%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-39,55%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-20,81%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-33,16%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-36,59%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-1,37%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-43,3%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-42,53%</t>
+          <t>-35,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-40,13%</t>
+          <t>-37,62%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-45,41; 11,58</t>
+          <t>-32,19; 41,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-54,44; -0,01</t>
+          <t>-64,08; -14,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,97; -3,72</t>
+          <t>-61,28; -8,3</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-28,93; 43,2</t>
+          <t>-46,71; 11,65</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-63,7; -14,02</t>
+          <t>-56,74; -4,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-62,85; -11,88</t>
+          <t>-56,65; -2,17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 13,8</t>
+          <t>-30,64; 13,27</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-53,27; -17,23</t>
+          <t>-52,34; -16,19</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-55,45; -18,78</t>
+          <t>-54,68; -19,02</t>
         </is>
       </c>
     </row>
